--- a/Data/Stage/GoalData.xlsx
+++ b/Data/Stage/GoalData.xlsx
@@ -8,17 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\Game\3DGame\Data\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A7D135-5CFD-49A1-8788-DE5E5E448903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC978B7-8CB4-44BD-81C0-2D8AB59A3EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="2355" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2970" yWindow="3810" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -28,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>posX</t>
   </si>
@@ -60,6 +69,17 @@
   </si>
   <si>
     <t>collisionSizeZ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>collisionOffSetX</t>
+  </si>
+  <si>
+    <t>collisionOffSetY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>collisionOffSetZ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -385,13 +405,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="7" max="9" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="15.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -419,16 +440,25 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:12">
       <c r="A2">
-        <v>150</v>
+        <v>3750</v>
       </c>
       <c r="B2">
         <v>150</v>
       </c>
       <c r="C2">
-        <v>150</v>
+        <v>590</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -443,10 +473,19 @@
         <v>150</v>
       </c>
       <c r="H2">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="I2">
         <v>150</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>150</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
